--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11486591</v>
+        <v>11478172</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11478172</v>
+        <v>11491223</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11491223</v>
+        <v>11487582</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11487582</v>
+        <v>11521595</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11521595</v>
+        <v>11519959</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11519959</v>
+        <v>11540553</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11540553</v>
+        <v>11534671</v>
       </c>
       <c r="D2" t="str">
         <v/>

--- a/client_gamedata/charAssets.xlsx
+++ b/client_gamedata/charAssets.xlsx
@@ -430,7 +430,7 @@
         <v>CharAssets.zip</v>
       </c>
       <c r="C2">
-        <v>11534671</v>
+        <v>11528732</v>
       </c>
       <c r="D2" t="str">
         <v/>
